--- a/data_analytics/forecast_analysis/results/results_table.xlsx
+++ b/data_analytics/forecast_analysis/results/results_table.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Работа\mgimo-foreign-trade\data_analytics\forecast_analysis\results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC22F4EB-1D86-4BF5-8A9B-21FAA70002BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -70,9 +76,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -85,6 +107,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -108,24 +131,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +196,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -197,6 +230,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -231,9 +265,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -406,11 +441,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,8 +481,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
@@ -447,7 +492,7 @@
         <v>0.496</v>
       </c>
       <c r="D2">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="E2">
         <v>1.478</v>
@@ -456,39 +501,39 @@
         <v>0.877</v>
       </c>
       <c r="G2">
-        <v>0.783</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="H2">
-        <v>3.425</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.667</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="C3">
-        <v>0.516</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="D3">
-        <v>0.446</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="E3">
-        <v>1.128</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="F3">
-        <v>0.894</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G3">
-        <v>0.783</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="H3">
-        <v>1.209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>1.2090000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -496,77 +541,77 @@
         <v>0.503</v>
       </c>
       <c r="C4">
-        <v>0.506</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="D4">
-        <v>0.447</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="E4">
-        <v>0.906</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="F4">
-        <v>0.901</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="G4">
-        <v>0.787</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="H4">
-        <v>29.173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
+        <v>29.172999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.775</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="C5">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="D5">
-        <v>0.447</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="E5">
-        <v>1.291</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="F5">
-        <v>1.487</v>
+        <v>1.4870000000000001</v>
       </c>
       <c r="G5">
-        <v>0.785</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="H5">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.517</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="C6">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="D6">
-        <v>0.448</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="E6">
-        <v>0.929</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="F6">
-        <v>0.905</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="G6">
-        <v>0.781</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="H6">
-        <v>48.826</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>48.826000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -574,16 +619,16 @@
         <v>0.495</v>
       </c>
       <c r="C7">
-        <v>0.519</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="D7">
-        <v>0.449</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="E7">
         <v>0.871</v>
       </c>
       <c r="F7">
-        <v>0.903</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="G7">
         <v>0.79</v>
@@ -592,7 +637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -603,22 +648,22 @@
         <v>0.52</v>
       </c>
       <c r="D8">
-        <v>0.451</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="E8">
-        <v>0.885</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="F8">
-        <v>0.926</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="G8">
-        <v>0.782</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="H8">
-        <v>39.648</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>39.648000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -626,51 +671,135 @@
         <v>0.49</v>
       </c>
       <c r="C9">
-        <v>0.519</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="D9">
-        <v>0.452</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="E9">
-        <v>0.865</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="F9">
-        <v>0.899</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="G9">
-        <v>0.792</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="H9">
-        <v>148.795</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
+        <v>148.79499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B10">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="C10">
-        <v>0.676</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="D10">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="E10">
-        <v>1.664</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="F10">
-        <v>1.225</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="G10">
-        <v>1.027</v>
+        <v>1.0269999999999999</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B10">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C10">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D10">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E10">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F10">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G10">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_analytics/forecast_analysis/results/results_table.xlsx
+++ b/data_analytics/forecast_analysis/results/results_table.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Работа\mgimo-foreign-trade\data_analytics\forecast_analysis\results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC22F4EB-1D86-4BF5-8A9B-21FAA70002BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>model</t>
   </si>
@@ -43,31 +37,61 @@
     <t>RMSE_2025</t>
   </si>
   <si>
+    <t>WMAE_Q1 2026</t>
+  </si>
+  <si>
+    <t>WMAE_Q4 2025</t>
+  </si>
+  <si>
+    <t>WMAE_2025</t>
+  </si>
+  <si>
     <t>Time_sec</t>
   </si>
   <si>
+    <t>ETS + DFM</t>
+  </si>
+  <si>
+    <t>Avg(SARIMA, ETS+DFM)</t>
+  </si>
+  <si>
+    <t>ETS</t>
+  </si>
+  <si>
+    <t>STL + DFM</t>
+  </si>
+  <si>
+    <t>SARIMA</t>
+  </si>
+  <si>
     <t>DFM</t>
   </si>
   <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>PCA + VAR</t>
+  </si>
+  <si>
+    <t>FADREG</t>
+  </si>
+  <si>
     <t>PCA + BVAR</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>PCA + VAR</t>
-  </si>
-  <si>
-    <t>FADREG</t>
-  </si>
-  <si>
     <t>Static</t>
   </si>
   <si>
+    <t>AR + COVID</t>
+  </si>
+  <si>
     <t>MA</t>
   </si>
   <si>
     <t>ARIMA</t>
+  </si>
+  <si>
+    <t>Seasonal naive</t>
   </si>
   <si>
     <t>Naive</t>
@@ -76,25 +100,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -107,7 +115,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -131,34 +138,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +193,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +227,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +261,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,21 +436,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.21875" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,326 +465,577 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
       <c r="B2">
-        <v>0.89</v>
+        <v>0.499</v>
       </c>
       <c r="C2">
+        <v>0.503</v>
+      </c>
+      <c r="D2">
+        <v>0.438</v>
+      </c>
+      <c r="E2">
+        <v>0.869</v>
+      </c>
+      <c r="F2">
+        <v>0.887</v>
+      </c>
+      <c r="G2">
+        <v>0.781</v>
+      </c>
+      <c r="H2">
+        <v>0.177</v>
+      </c>
+      <c r="I2">
+        <v>0.172</v>
+      </c>
+      <c r="J2">
+        <v>0.145</v>
+      </c>
+      <c r="K2">
+        <v>19.044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>0.483</v>
+      </c>
+      <c r="C3">
         <v>0.496</v>
       </c>
-      <c r="D2">
-        <v>0.44500000000000001</v>
-      </c>
-      <c r="E2">
-        <v>1.478</v>
-      </c>
-      <c r="F2">
-        <v>0.877</v>
-      </c>
-      <c r="G2">
-        <v>0.78300000000000003</v>
-      </c>
-      <c r="H2">
-        <v>3.4249999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="C3">
-        <v>0.51600000000000001</v>
-      </c>
       <c r="D3">
-        <v>0.44600000000000001</v>
+        <v>0.439</v>
       </c>
       <c r="E3">
-        <v>1.1279999999999999</v>
+        <v>0.849</v>
       </c>
       <c r="F3">
-        <v>0.89400000000000002</v>
+        <v>0.873</v>
       </c>
       <c r="G3">
-        <v>0.78300000000000003</v>
+        <v>0.777</v>
       </c>
       <c r="H3">
-        <v>1.2090000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0.17</v>
+      </c>
+      <c r="I3">
+        <v>0.17</v>
+      </c>
+      <c r="J3">
+        <v>0.145</v>
+      </c>
+      <c r="K3">
+        <v>128.717</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.503</v>
       </c>
       <c r="C4">
-        <v>0.50600000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="D4">
-        <v>0.44700000000000001</v>
+        <v>0.439</v>
       </c>
       <c r="E4">
-        <v>0.90600000000000003</v>
+        <v>0.885</v>
       </c>
       <c r="F4">
-        <v>0.90100000000000002</v>
+        <v>0.901</v>
       </c>
       <c r="G4">
-        <v>0.78700000000000003</v>
+        <v>0.783</v>
       </c>
       <c r="H4">
-        <v>29.172999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>0.169</v>
+      </c>
+      <c r="I4">
+        <v>0.175</v>
+      </c>
+      <c r="J4">
+        <v>0.145</v>
+      </c>
+      <c r="K4">
+        <v>15.81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>0.77500000000000002</v>
+        <v>0.539</v>
       </c>
       <c r="C5">
-        <v>0.93600000000000005</v>
+        <v>0.504</v>
       </c>
       <c r="D5">
-        <v>0.44700000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="E5">
-        <v>1.2909999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F5">
-        <v>1.4870000000000001</v>
+        <v>0.919</v>
       </c>
       <c r="G5">
-        <v>0.78500000000000003</v>
+        <v>0.801</v>
       </c>
       <c r="H5">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>0.179</v>
+      </c>
+      <c r="I5">
+        <v>0.176</v>
+      </c>
+      <c r="J5">
+        <v>0.141</v>
+      </c>
+      <c r="K5">
+        <v>3.302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>0.51700000000000002</v>
+        <v>0.496</v>
       </c>
       <c r="C6">
-        <v>0.50800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>0.44800000000000001</v>
+        <v>0.447</v>
       </c>
       <c r="E6">
-        <v>0.92900000000000005</v>
+        <v>0.908</v>
       </c>
       <c r="F6">
-        <v>0.90500000000000003</v>
+        <v>0.884</v>
       </c>
       <c r="G6">
-        <v>0.78100000000000003</v>
+        <v>0.791</v>
       </c>
       <c r="H6">
-        <v>48.826000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0.168</v>
+      </c>
+      <c r="I6">
+        <v>0.17</v>
+      </c>
+      <c r="J6">
+        <v>0.147</v>
+      </c>
+      <c r="K6">
+        <v>109.674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0.509</v>
+      </c>
+      <c r="D7">
+        <v>0.447</v>
+      </c>
+      <c r="E7">
+        <v>0.866</v>
+      </c>
+      <c r="F7">
+        <v>0.891</v>
+      </c>
+      <c r="G7">
+        <v>0.788</v>
+      </c>
+      <c r="H7">
+        <v>0.18</v>
+      </c>
+      <c r="I7">
+        <v>0.179</v>
+      </c>
+      <c r="J7">
+        <v>0.151</v>
+      </c>
+      <c r="K7">
+        <v>3.273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>0.503</v>
+      </c>
+      <c r="C8">
+        <v>0.506</v>
+      </c>
+      <c r="D8">
+        <v>0.447</v>
+      </c>
+      <c r="E8">
+        <v>0.906</v>
+      </c>
+      <c r="F8">
+        <v>0.901</v>
+      </c>
+      <c r="G8">
+        <v>0.787</v>
+      </c>
+      <c r="H8">
+        <v>0.18</v>
+      </c>
+      <c r="I8">
+        <v>0.171</v>
+      </c>
+      <c r="J8">
+        <v>0.149</v>
+      </c>
+      <c r="K8">
+        <v>29.051</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>0.775</v>
+      </c>
+      <c r="C9">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="D9">
+        <v>0.447</v>
+      </c>
+      <c r="E9">
+        <v>1.291</v>
+      </c>
+      <c r="F9">
+        <v>1.487</v>
+      </c>
+      <c r="G9">
+        <v>0.785</v>
+      </c>
+      <c r="H9">
+        <v>0.258</v>
+      </c>
+      <c r="I9">
+        <v>0.337</v>
+      </c>
+      <c r="J9">
+        <v>0.153</v>
+      </c>
+      <c r="K9">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>0.517</v>
+      </c>
+      <c r="C10">
+        <v>0.508</v>
+      </c>
+      <c r="D10">
+        <v>0.448</v>
+      </c>
+      <c r="E10">
+        <v>0.929</v>
+      </c>
+      <c r="F10">
+        <v>0.905</v>
+      </c>
+      <c r="G10">
+        <v>0.781</v>
+      </c>
+      <c r="H10">
+        <v>0.192</v>
+      </c>
+      <c r="I10">
+        <v>0.173</v>
+      </c>
+      <c r="J10">
+        <v>0.151</v>
+      </c>
+      <c r="K10">
+        <v>47.897</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>0.668</v>
+      </c>
+      <c r="C11">
+        <v>0.514</v>
+      </c>
+      <c r="D11">
+        <v>0.448</v>
+      </c>
+      <c r="E11">
+        <v>1.13</v>
+      </c>
+      <c r="F11">
+        <v>0.895</v>
+      </c>
+      <c r="G11">
+        <v>0.787</v>
+      </c>
+      <c r="H11">
+        <v>0.233</v>
+      </c>
+      <c r="I11">
+        <v>0.178</v>
+      </c>
+      <c r="J11">
+        <v>0.153</v>
+      </c>
+      <c r="K11">
+        <v>1.208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
         <v>0.495</v>
       </c>
-      <c r="C7">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="D7">
-        <v>0.44900000000000001</v>
-      </c>
-      <c r="E7">
+      <c r="C12">
+        <v>0.519</v>
+      </c>
+      <c r="D12">
+        <v>0.449</v>
+      </c>
+      <c r="E12">
         <v>0.871</v>
       </c>
-      <c r="F7">
-        <v>0.90300000000000002</v>
-      </c>
-      <c r="G7">
+      <c r="F12">
+        <v>0.903</v>
+      </c>
+      <c r="G12">
         <v>0.79</v>
       </c>
-      <c r="H7">
+      <c r="H12">
+        <v>0.172</v>
+      </c>
+      <c r="I12">
+        <v>0.18</v>
+      </c>
+      <c r="J12">
+        <v>0.152</v>
+      </c>
+      <c r="K12">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>0.51</v>
+      </c>
+      <c r="C13">
+        <v>0.51</v>
+      </c>
+      <c r="D13">
+        <v>0.449</v>
+      </c>
+      <c r="E13">
+        <v>0.919</v>
+      </c>
+      <c r="F13">
+        <v>0.904</v>
+      </c>
+      <c r="G13">
+        <v>0.788</v>
+      </c>
+      <c r="H13">
+        <v>0.181</v>
+      </c>
+      <c r="I13">
+        <v>0.173</v>
+      </c>
+      <c r="J13">
+        <v>0.149</v>
+      </c>
+      <c r="K13">
+        <v>35.297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
         <v>0.502</v>
       </c>
-      <c r="C8">
+      <c r="C14">
         <v>0.52</v>
       </c>
-      <c r="D8">
-        <v>0.45100000000000001</v>
-      </c>
-      <c r="E8">
-        <v>0.88500000000000001</v>
-      </c>
-      <c r="F8">
-        <v>0.92600000000000005</v>
-      </c>
-      <c r="G8">
-        <v>0.78200000000000003</v>
-      </c>
-      <c r="H8">
-        <v>39.648000000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
+      <c r="D14">
+        <v>0.451</v>
+      </c>
+      <c r="E14">
+        <v>0.885</v>
+      </c>
+      <c r="F14">
+        <v>0.926</v>
+      </c>
+      <c r="G14">
+        <v>0.782</v>
+      </c>
+      <c r="H14">
+        <v>0.175</v>
+      </c>
+      <c r="I14">
+        <v>0.175</v>
+      </c>
+      <c r="J14">
+        <v>0.15</v>
+      </c>
+      <c r="K14">
+        <v>39.387</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
         <v>0.49</v>
       </c>
-      <c r="C9">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="D9">
-        <v>0.45200000000000001</v>
-      </c>
-      <c r="E9">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="F9">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="G9">
-        <v>0.79200000000000004</v>
-      </c>
-      <c r="H9">
-        <v>148.79499999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>0.90900000000000003</v>
-      </c>
-      <c r="C10">
-        <v>0.67600000000000005</v>
-      </c>
-      <c r="D10">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="E10">
-        <v>1.6639999999999999</v>
-      </c>
-      <c r="F10">
-        <v>1.2250000000000001</v>
-      </c>
-      <c r="G10">
-        <v>1.0269999999999999</v>
-      </c>
-      <c r="H10">
+      <c r="C15">
+        <v>0.519</v>
+      </c>
+      <c r="D15">
+        <v>0.452</v>
+      </c>
+      <c r="E15">
+        <v>0.865</v>
+      </c>
+      <c r="F15">
+        <v>0.899</v>
+      </c>
+      <c r="G15">
+        <v>0.792</v>
+      </c>
+      <c r="H15">
+        <v>0.173</v>
+      </c>
+      <c r="I15">
+        <v>0.172</v>
+      </c>
+      <c r="J15">
+        <v>0.156</v>
+      </c>
+      <c r="K15">
+        <v>147.164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>0.656</v>
+      </c>
+      <c r="C16">
+        <v>0.601</v>
+      </c>
+      <c r="D16">
+        <v>0.576</v>
+      </c>
+      <c r="E16">
+        <v>1.155</v>
+      </c>
+      <c r="F16">
+        <v>1.211</v>
+      </c>
+      <c r="G16">
+        <v>1.08</v>
+      </c>
+      <c r="H16">
+        <v>0.206</v>
+      </c>
+      <c r="I16">
+        <v>0.179</v>
+      </c>
+      <c r="J16">
+        <v>0.175</v>
+      </c>
+      <c r="K16">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>0.909</v>
+      </c>
+      <c r="C17">
+        <v>0.676</v>
+      </c>
+      <c r="D17">
+        <v>0.599</v>
+      </c>
+      <c r="E17">
+        <v>1.664</v>
+      </c>
+      <c r="F17">
+        <v>1.225</v>
+      </c>
+      <c r="G17">
+        <v>1.027</v>
+      </c>
+      <c r="H17">
+        <v>0.278</v>
+      </c>
+      <c r="I17">
+        <v>0.217</v>
+      </c>
+      <c r="J17">
+        <v>0.197</v>
+      </c>
+      <c r="K17">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B10">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C10">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>